--- a/test/companydoc.xlsx
+++ b/test/companydoc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A409C59-A930-4986-981D-973682C91C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265C6BB8-4401-4ABB-92D7-B0C5EE243D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,9 +49,6 @@
     <t>user1</t>
   </si>
   <si>
-    <t>pass1</t>
-  </si>
-  <si>
     <t>Initial document</t>
   </si>
   <si>
@@ -59,13 +56,16 @@
   </si>
   <si>
     <t>pan</t>
+  </si>
+  <si>
+    <t>pass@123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,6 +77,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -114,16 +122,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -457,25 +468,28 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{4C5ACAC1-1C6C-48C4-A303-F869FC4177FA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>